--- a/models/6857_DCF_Model_20260906.xlsx
+++ b/models/6857_DCF_Model_20260906.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ryosuke0923\ryosuke-japanese-equity-research\models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12F1EA7A-3A48-46CA-B0D9-BECBFB0721E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6E5B28D-8A1C-457E-AC78-AD9118CB242C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="423" uniqueCount="339">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="429" uniqueCount="344">
   <si>
     <t>DISCLAIMER: This is a sample analysis for demonstration purposes only. It does not constitute investment advice.</t>
   </si>
@@ -771,7 +771,7 @@
     <t>-</t>
   </si>
   <si>
-    <t>Generated by pipeline on 2026-09-06 19:19, template rev 63983ab</t>
+    <t>Generated by pipeline on 2026-09-06 21:08, template rev b29b23d</t>
   </si>
   <si>
     <t>初期生成（手修正なし）</t>
@@ -795,6 +795,21 @@
     <t>確定</t>
   </si>
   <si>
+    <t>Executive Summary!C10</t>
+  </si>
+  <si>
+    <t>Exit法を[参考]に降格 → Target = PGM 単独（C10 は C16 を参照）</t>
+  </si>
+  <si>
+    <t>【追補6 §X】PGMとExitの乖離が **6.08倍** で 3.0倍を超えたため、**乖離そのものを裁定トリガーとする追補6 §X により中点平均を禁止**し、どちらの脚を落とすかを判定した。■**観測倍率バンドテスト**: Peer の実測 EV/EBITDA の第1〜第3四分位バンドは **—倍**。これに対し **PGM逆算 5.08倍 / 仮定Exit 30.90倍**。**Exit法のみがバンドの外にあるため Exit法を[参考]に降格し、Target = PGM 単独**とした。■バンドテストは市場倍率を無条件のアンカーにするものではない（それではスクリーナーが市場の複写に堕する）。**実際に取引されているレンジの外に出た脚だけを取り除く**という位置づけである。</t>
+  </si>
+  <si>
+    <t>PGM/Exit の中点平均</t>
+  </si>
+  <si>
+    <t>裁定適用（追補6 §X）</t>
+  </si>
+  <si>
     <t>Pipeline Metadata (do not edit — read by scripts/validate_output.py)</t>
   </si>
   <si>
@@ -975,7 +990,7 @@
     <t>generated_at</t>
   </si>
   <si>
-    <t>2026-09-06 19:19:40</t>
+    <t>2026-09-06 21:08:01</t>
   </si>
   <si>
     <t>guidance_note</t>
@@ -1047,7 +1062,7 @@
     <t>template_rev</t>
   </si>
   <si>
-    <t>63983ab</t>
+    <t>b29b23d</t>
   </si>
   <si>
     <t>ticker</t>
@@ -6295,86 +6310,106 @@
         <v>252</v>
       </c>
     </row>
+    <row r="7" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B7" t="s">
+        <v>243</v>
+      </c>
+      <c r="C7" t="s">
+        <v>253</v>
+      </c>
+      <c r="D7" t="s">
+        <v>254</v>
+      </c>
+      <c r="E7" t="s">
+        <v>255</v>
+      </c>
+      <c r="F7" t="s">
+        <v>256</v>
+      </c>
+      <c r="G7" t="s">
+        <v>257</v>
+      </c>
+    </row>
     <row r="12" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B12" s="8" t="s">
-        <v>253</v>
+        <v>258</v>
       </c>
     </row>
     <row r="13" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B13" s="10" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="C13" s="10" t="s">
-        <v>255</v>
+        <v>260</v>
       </c>
     </row>
     <row r="14" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B14" s="4" t="s">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="C14" t="s">
-        <v>257</v>
+        <v>262</v>
       </c>
     </row>
     <row r="15" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B15" s="4" t="s">
-        <v>258</v>
+        <v>263</v>
       </c>
       <c r="C15" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
     </row>
     <row r="16" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B16" s="4" t="s">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="C16" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
     </row>
     <row r="17" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B17" s="4" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="C17" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
     </row>
     <row r="18" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B18" s="4" t="s">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="C18" t="s">
-        <v>264</v>
+        <v>269</v>
       </c>
     </row>
     <row r="19" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B19" s="4" t="s">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="C19" t="s">
-        <v>266</v>
+        <v>271</v>
       </c>
     </row>
     <row r="20" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B20" s="4" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="C20" t="s">
-        <v>268</v>
+        <v>273</v>
       </c>
     </row>
     <row r="21" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B21" s="4" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="C21" t="s">
-        <v>270</v>
+        <v>275</v>
       </c>
     </row>
     <row r="22" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B22" s="4" t="s">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c r="C22" t="s">
         <v>41</v>
@@ -6382,7 +6417,7 @@
     </row>
     <row r="23" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B23" s="4" t="s">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="C23" t="s">
         <v>4</v>
@@ -6390,7 +6425,7 @@
     </row>
     <row r="24" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B24" s="4" t="s">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="C24" t="s">
         <v>243</v>
@@ -6398,287 +6433,287 @@
     </row>
     <row r="25" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B25" s="4" t="s">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="C25" t="s">
-        <v>275</v>
+        <v>280</v>
       </c>
     </row>
     <row r="26" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B26" s="4" t="s">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="C26" t="s">
-        <v>264</v>
+        <v>269</v>
       </c>
     </row>
     <row r="27" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B27" s="4" t="s">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="C27" t="s">
-        <v>264</v>
+        <v>269</v>
       </c>
     </row>
     <row r="28" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B28" s="4" t="s">
-        <v>278</v>
+        <v>283</v>
       </c>
       <c r="C28" t="s">
-        <v>279</v>
+        <v>284</v>
       </c>
     </row>
     <row r="29" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B29" s="4" t="s">
-        <v>280</v>
+        <v>285</v>
       </c>
       <c r="C29" t="s">
-        <v>281</v>
+        <v>286</v>
       </c>
     </row>
     <row r="30" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B30" s="4" t="s">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="C30" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
     </row>
     <row r="31" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B31" s="4" t="s">
+        <v>289</v>
+      </c>
+      <c r="C31" t="s">
         <v>284</v>
-      </c>
-      <c r="C31" t="s">
-        <v>279</v>
       </c>
     </row>
     <row r="32" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B32" s="4" t="s">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="C32" t="s">
-        <v>264</v>
+        <v>269</v>
       </c>
     </row>
     <row r="33" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B33" s="4" t="s">
-        <v>286</v>
+        <v>291</v>
       </c>
       <c r="C33" t="s">
-        <v>275</v>
+        <v>280</v>
       </c>
     </row>
     <row r="34" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B34" s="4" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="C34" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
     </row>
     <row r="35" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B35" s="4" t="s">
-        <v>289</v>
+        <v>294</v>
       </c>
       <c r="C35" t="s">
-        <v>290</v>
+        <v>295</v>
       </c>
     </row>
     <row r="36" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B36" s="4" t="s">
-        <v>291</v>
+        <v>296</v>
       </c>
       <c r="C36" t="s">
-        <v>292</v>
+        <v>297</v>
       </c>
     </row>
     <row r="37" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B37" s="4" t="s">
-        <v>293</v>
+        <v>298</v>
       </c>
       <c r="C37" t="s">
-        <v>294</v>
+        <v>299</v>
       </c>
     </row>
     <row r="38" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B38" s="4" t="s">
-        <v>295</v>
+        <v>300</v>
       </c>
       <c r="C38" t="s">
-        <v>296</v>
+        <v>301</v>
       </c>
     </row>
     <row r="39" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B39" s="4" t="s">
-        <v>297</v>
+        <v>302</v>
       </c>
       <c r="C39" t="s">
-        <v>298</v>
+        <v>303</v>
       </c>
     </row>
     <row r="40" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B40" s="4" t="s">
-        <v>299</v>
+        <v>304</v>
       </c>
       <c r="C40" t="s">
-        <v>268</v>
+        <v>273</v>
       </c>
     </row>
     <row r="41" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B41" s="4" t="s">
-        <v>300</v>
+        <v>305</v>
       </c>
       <c r="C41" t="s">
-        <v>301</v>
+        <v>306</v>
       </c>
     </row>
     <row r="42" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B42" s="4" t="s">
-        <v>302</v>
+        <v>307</v>
       </c>
       <c r="C42" t="s">
-        <v>303</v>
+        <v>308</v>
       </c>
     </row>
     <row r="43" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B43" s="4" t="s">
-        <v>304</v>
+        <v>309</v>
       </c>
       <c r="C43" t="s">
-        <v>305</v>
+        <v>310</v>
       </c>
     </row>
     <row r="44" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B44" s="4" t="s">
-        <v>306</v>
+        <v>311</v>
       </c>
       <c r="C44" t="s">
-        <v>307</v>
+        <v>312</v>
       </c>
     </row>
     <row r="45" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B45" s="4" t="s">
-        <v>308</v>
+        <v>313</v>
       </c>
       <c r="C45" t="s">
-        <v>309</v>
+        <v>314</v>
       </c>
     </row>
     <row r="46" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B46" s="4" t="s">
-        <v>310</v>
+        <v>315</v>
       </c>
       <c r="C46" t="s">
-        <v>311</v>
+        <v>316</v>
       </c>
     </row>
     <row r="47" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B47" s="4" t="s">
-        <v>312</v>
+        <v>317</v>
       </c>
       <c r="C47" t="s">
-        <v>313</v>
+        <v>318</v>
       </c>
     </row>
     <row r="48" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B48" s="4" t="s">
-        <v>314</v>
+        <v>319</v>
       </c>
       <c r="C48" t="s">
-        <v>315</v>
+        <v>320</v>
       </c>
     </row>
     <row r="49" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B49" s="4" t="s">
-        <v>316</v>
+        <v>321</v>
       </c>
       <c r="C49" t="s">
-        <v>317</v>
+        <v>322</v>
       </c>
     </row>
     <row r="50" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B50" s="4" t="s">
-        <v>318</v>
+        <v>323</v>
       </c>
       <c r="C50" t="s">
-        <v>319</v>
+        <v>324</v>
       </c>
     </row>
     <row r="51" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B51" s="4" t="s">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="C51" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
     </row>
     <row r="52" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B52" s="4" t="s">
-        <v>322</v>
+        <v>327</v>
       </c>
       <c r="C52" t="s">
-        <v>323</v>
+        <v>328</v>
       </c>
     </row>
     <row r="53" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B53" s="4" t="s">
-        <v>324</v>
+        <v>329</v>
       </c>
       <c r="C53" t="s">
-        <v>325</v>
+        <v>330</v>
       </c>
     </row>
     <row r="54" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B54" s="4" t="s">
-        <v>326</v>
+        <v>331</v>
       </c>
       <c r="C54" t="s">
-        <v>327</v>
+        <v>332</v>
       </c>
     </row>
     <row r="55" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B55" s="4" t="s">
-        <v>328</v>
+        <v>333</v>
       </c>
       <c r="C55" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
     </row>
     <row r="56" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B56" s="4" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="C56" t="s">
-        <v>331</v>
+        <v>336</v>
       </c>
     </row>
     <row r="57" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B57" s="4" t="s">
-        <v>332</v>
+        <v>337</v>
       </c>
       <c r="C57" t="s">
-        <v>333</v>
+        <v>338</v>
       </c>
     </row>
     <row r="58" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B58" s="4" t="s">
-        <v>334</v>
+        <v>339</v>
       </c>
       <c r="C58" t="s">
-        <v>335</v>
+        <v>340</v>
       </c>
     </row>
     <row r="59" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B59" s="4" t="s">
-        <v>336</v>
+        <v>341</v>
       </c>
       <c r="C59" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
     </row>
     <row r="60" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B60" s="4" t="s">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="C60" t="s">
         <v>206</v>
